--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,12 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560670.4044435194</v>
+        <v>560670</v>
       </c>
       <c r="R4" t="n">
-        <v>6392859.505945046</v>
+        <v>6392860</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +981,9 @@
           <t>1978-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8411-2021 artfynd.xlsx
+++ b/artfynd/A 8411-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>73968086</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
